--- a/Luban/Config/Datas/Levels/L18/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L18/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L18 W1/25; N=48; EHP=299.904000; normal:17x24,normal:18x24</t>
+          <t>L18 W1/25; N=48; EHP=756.325272; normal:17x24,normal:18x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L18 W2/25; N=54; EHP=353.283163; normal:17x27,normal:18x27</t>
+          <t>L18 W2/25; N=54; EHP=890.941716; normal:17x27,normal:18x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3784136,3784673,3784019,3784136,3784673,3784019,3784136,3784673,3784091,3784136,3784673,3784099,3784136,3784673,3784099,3784136,3784673,3784107,3784136,3784673,3784115,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784136,3784136,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144</t>
+          <t>3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784136,3784136,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784136,3784136,3784136,3784136,3784136,3784136,3784136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L18 W3/25; N=60; EHP=434.260992; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x19,normal:18x18,swarm:84x16</t>
+          <t>L18 W3/25; N=60; EHP=1178.568729; normal:17x26,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3786136,3786673,3786019,3786136,3786673,3786019,3786136,3786673,3786091,3786136,3786673,3786091,3786136,3786673,3786099,3786136,3786673,3786107,3786136,3786673,3786107,3786136,3786673,3786115,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786136,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144</t>
+          <t>3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786136,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786136,3786136,3786136,3786136,3786136,3786136,3786136,3786136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L18 W4/25; N=66; EHP=550.057675; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x20,normal:18x20,swarm:84x18</t>
+          <t>L18 W4/25; N=66; EHP=1497.558453; normal:17x28,normal:18x20,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3788136,3788673,3788019,3788668,3788136,3788673,3788091,3788668,3788136,3788673,3788091,3788668,3788136,3788673,3788099,3788868,3788136,3788673,3788099,3788868,3788136,3788673,3788107,3788868,3788136,3788673,3788107,3788868,3788136,3788673,3788115,3788988,3788136,3788673,3788115,3788988,3788136,3788673,3788988,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788144,3788673,3788144,3788673,3788144,3788673,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144</t>
+          <t>3788136,3788019,3788019,3788668,3788136,3788091,3788091,3788668,3788136,3788091,3788091,3788668,3788136,3788099,3788099,3788868,3788136,3788099,3788099,3788868,3788136,3788107,3788107,3788868,3788136,3788107,3788107,3788868,3788136,3788115,3788115,3788988,3788136,3788115,3788115,3788988,3788136,3788673,3788988,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788144,3788673,3788144,3788673,3788144,3788673,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L18 W5/25; N=72; EHP=1033.524366; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x17,normal:18x16,medium:83x3,swarm:84x20,medium:108x4,medium:123x3</t>
+          <t>L18 W5/25; N=72; EHP=2641.421770; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x3,medium:108x4,medium:123x3,normal:17x17,normal:18x16,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3790136,3790673,3790242,3790019,3790668,3790136,3790673,3790242,3790019,3790668,3790136,3790673,3790242,3790091,3790668,3790136,3790673,3790466,3790091,3790668,3790136,3790673,3790466,3790099,3790868,3790136,3790673,3790514,3790099,3790868,3790136,3790673,3790514,3790107,3790868,3790136,3790673,3790786,3790115,3790988,3790136,3790673,3790786,3790115,3790988,3790136,3790673,3790988,3790136,3790673,3790988,3790136,3790673,3790136,3790673,3790136,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790144,3790144,3790144,3790144,3790144,3790144</t>
+          <t>3790136,3790019,3790242,3790019,3790668,3790136,3790019,3790242,3790019,3790668,3790136,3790091,3790242,3790091,3790668,3790136,3790091,3790466,3790091,3790668,3790136,3790099,3790466,3790099,3790868,3790136,3790099,3790514,3790099,3790868,3790136,3790107,3790514,3790107,3790868,3790136,3790115,3790786,3790115,3790988,3790136,3790115,3790786,3790115,3790988,3790136,3790673,3790988,3790136,3790673,3790988,3790136,3790673,3790136,3790673,3790136,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790673,3790144,3790144,3790144,3790144,3790144,3790144,3790144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L18 W6/25; N=78; EHP=1055.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x14,normal:18x14,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x21,fast:98x2,medium:108x3,medium:123x4</t>
+          <t>L18 W6/25; N=78; EHP=2693.829625; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x2,medium:83x4,medium:108x3,medium:123x4,normal:17x14,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3792136,3792673,3792242,3792019,3792668,3792136,3792673,3792242,3792019,3792668,3792136,3792673,3792466,3792091,3792668,3792136,3792673,3792466,3792091,3792668,3792136,3792673,3792466,3792099,3792868,3792136,3792673,3792514,3792099,3792868,3792136,3792673,3792514,3792107,3792868,3792136,3792673,3792786,3792107,3792868,3792136,3792673,3792786,3792115,3792988,3792136,3792673,3792786,3792115,3792988,3792136,3792673,3792988,3792136,3792673,3792988,3792136,3792673,3792136,3792673,3792136,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792144,3792144,3792144,3792144,3792144</t>
+          <t>3792136,3792019,3792242,3792019,3792668,3792136,3792019,3792242,3792019,3792668,3792136,3792091,3792466,3792091,3792668,3792136,3792091,3792466,3792091,3792668,3792136,3792099,3792466,3792099,3792868,3792136,3792099,3792514,3792099,3792868,3792136,3792107,3792514,3792107,3792868,3792136,3792107,3792786,3792107,3792868,3792136,3792115,3792786,3792115,3792988,3792136,3792115,3792786,3792115,3792988,3792136,3792673,3792988,3792136,3792673,3792988,3792136,3792673,3792136,3792673,3792136,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792673,3792144,3792144,3792144,3792144,3792144,3792144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L18 W7/25; N=84; EHP=1184.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x14,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x23,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L18 W7/25; N=84; EHP=3024.521939; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3794136,3794673,3794242,3794019,3794668,3794136,3794673,3794242,3794019,3794668,3794136,3794673,3794466,3794091,3794668,3794136,3794673,3794466,3794091,3794668,3794136,3794673,3794466,3794099,3794868,3794136,3794673,3794514,3794099,3794868,3794136,3794673,3794514,3794099,3794868,3794136,3794673,3794514,3794107,3794868,3794136,3794673,3794786,3794107,3794868,3794136,3794673,3794786,3794115,3794988,3794136,3794673,3794115,3794988,3794136,3794673,3794988,3794136,3794673,3794988,3794136,3794673,3794136,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794144,3794144,3794144,3794144,3794144</t>
+          <t>3794136,3794019,3794242,3794019,3794668,3794136,3794019,3794242,3794019,3794668,3794136,3794091,3794466,3794091,3794668,3794136,3794091,3794466,3794091,3794668,3794136,3794099,3794466,3794099,3794868,3794136,3794099,3794514,3794099,3794868,3794136,3794099,3794514,3794099,3794868,3794136,3794107,3794514,3794107,3794868,3794136,3794107,3794786,3794107,3794868,3794136,3794115,3794786,3794115,3794988,3794136,3794115,3794115,3794988,3794136,3794673,3794988,3794136,3794673,3794988,3794136,3794673,3794136,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794673,3794144,3794144,3794144,3794144,3794144,3794144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L18 W8/25; N=90; EHP=1522.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x15,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x25,fast:98x2,medium:108x5,medium:123x4</t>
+          <t>L18 W8/25; N=90; EHP=3889.310629; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x5,medium:123x4,normal:17x15,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3796136,3796673,3796242,3796019,3796668,3796136,3796673,3796242,3796019,3796668,3796136,3796673,3796242,3796019,3796668,3796136,3796673,3796466,3796091,3796668,3796136,3796673,3796466,3796091,3796668,3796136,3796673,3796514,3796099,3796868,3796136,3796673,3796514,3796099,3796868,3796136,3796673,3796514,3796107,3796868,3796136,3796673,3796786,3796107,3796868,3796136,3796673,3796786,3796107,3796988,3796136,3796673,3796786,3796115,3796988,3796136,3796673,3796115,3796988,3796136,3796673,3796988,3796136,3796673,3796988,3796136,3796673,3796136,3796673,3796136,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796144,3796144,3796144,3796144,3796144,3796144</t>
+          <t>3796136,3796019,3796242,3796019,3796668,3796136,3796019,3796242,3796019,3796668,3796136,3796019,3796242,3796019,3796668,3796136,3796091,3796466,3796091,3796668,3796136,3796091,3796466,3796091,3796668,3796136,3796099,3796514,3796099,3796868,3796136,3796099,3796514,3796099,3796868,3796136,3796107,3796514,3796107,3796868,3796136,3796107,3796786,3796107,3796868,3796136,3796107,3796786,3796107,3796988,3796136,3796115,3796786,3796115,3796988,3796136,3796115,3796115,3796988,3796136,3796673,3796988,3796136,3796673,3796988,3796136,3796673,3796136,3796673,3796136,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796673,3796144,3796144,3796144,3796144,3796144,3796144,3796144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L18 W9/25; N=96; EHP=1943.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x16,fast:30x3,fast:58x2,fast:64x3,medium:83x5,swarm:84x26,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L18 W9/25; N=96; EHP=4966.513396; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x3,medium:83x5,medium:108x4,medium:123x5,normal:17x17,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3798136,3798673,3798242,3798019,3798668,3798136,3798673,3798242,3798019,3798668,3798136,3798673,3798242,3798091,3798668,3798136,3798673,3798466,3798091,3798668,3798136,3798673,3798466,3798091,3798668,3798136,3798673,3798466,3798099,3798868,3798136,3798673,3798514,3798099,3798868,3798136,3798673,3798514,3798107,3798868,3798136,3798673,3798514,3798107,3798868,3798136,3798673,3798786,3798107,3798868,3798136,3798673,3798786,3798115,3798988,3798136,3798673,3798786,3798115,3798988,3798136,3798673,3798988,3798136,3798673,3798988,3798136,3798673,3798988,3798136,3798673,3798136,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798144,3798144,3798144,3798144,3798144,3798144</t>
+          <t>3798136,3798019,3798242,3798019,3798668,3798136,3798019,3798242,3798019,3798668,3798136,3798091,3798242,3798091,3798668,3798136,3798091,3798466,3798091,3798668,3798136,3798091,3798466,3798091,3798668,3798136,3798099,3798466,3798099,3798868,3798136,3798099,3798514,3798099,3798868,3798136,3798107,3798514,3798107,3798868,3798136,3798107,3798514,3798107,3798868,3798136,3798107,3798786,3798107,3798868,3798136,3798115,3798786,3798115,3798988,3798136,3798115,3798786,3798115,3798988,3798136,3798673,3798988,3798136,3798673,3798988,3798136,3798673,3798988,3798136,3798673,3798136,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798673,3798144,3798144,3798144,3798144,3798144,3798144,3798144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L18 W10/25; N=102; EHP=3582.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L18 W10/25; N=102; EHP=9148.367752; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x17,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3800136,3800673,3800242,3800019,3800668,3800253,3800136,3800673,3800242,3800019,3800668,3800325,3800136,3800673,3800242,3800091,3800668,3800541,3800136,3800673,3800466,3800091,3800668,3800565,3800136,3800673,3800466,3800091,3800668,3800565,3800136,3800673,3800466,3800099,3800868,3800645,3800136,3800673,3800514,3800099,3800868,3800693,3800136,3800673,3800514,3800099,3800868,3800709,3800136,3800673,3800514,3800107,3800868,3801021,3800136,3800673,3800786,3800107,3800868,3801021,3800136,3800673,3800786,3800115,3800868,3800136,3800673,3800786,3800115,3800988,3800136,3800673,3800115,3800988,3800136,3800673,3800988,3800144,3800673,3800988,3800144,3800673,3800988,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800673,3800673,3800673</t>
+          <t>3800136,3800019,3800242,3800019,3800668,3800253,3800136,3800019,3800242,3800019,3800668,3800325,3800136,3800091,3800242,3800091,3800668,3800541,3800136,3800091,3800466,3800091,3800668,3800565,3800136,3800091,3800466,3800091,3800668,3800565,3800136,3800099,3800466,3800099,3800868,3800645,3800136,3800099,3800514,3800099,3800868,3800693,3800136,3800099,3800514,3800099,3800868,3800709,3800136,3800107,3800514,3800107,3800868,3801021,3800136,3800107,3800786,3800107,3800868,3801021,3800136,3800115,3800786,3800115,3800868,3800136,3800115,3800786,3800115,3800988,3800136,3800115,3800115,3800988,3800136,3800673,3800988,3800144,3800673,3800988,3800144,3800673,3800988,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800144,3800673,3800673,3800673,3800673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L18 W11/25; N=108; EHP=3654.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x13,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x5,swarm:84x30,heavy:86x1,heavy:88x1,fast:98x3,medium:108x6,medium:123x5,heavy:127x2</t>
+          <t>L18 W11/25; N=108; EHP=9322.189605; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x5,medium:108x6,medium:123x5,normal:17x14,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3802136,3802673,3802242,3802019,3802668,3802253,3802136,3802673,3802242,3802019,3802668,3802325,3802136,3802673,3802242,3802019,3802668,3802541,3802136,3802673,3802466,3802091,3802668,3802541,3802136,3802673,3802466,3802091,3802668,3802565,3802136,3802673,3802466,3802099,3802668,3802565,3802136,3802673,3802466,3802099,3802868,3802645,3802136,3802673,3802514,3802099,3802868,3802693,3802136,3802673,3802514,3802107,3802868,3802709,3802136,3802673,3802514,3802107,3802868,3802709,3802136,3802673,3802786,3802107,3802868,3803021,3802136,3802673,3802786,3802115,3802988,3802136,3802673,3802786,3802115,3802988,3802136,3802673,3802115,3802988,3802144,3802673,3802988,3802144,3802673,3802988,3802144,3802673,3802988,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802673,3802673,3802673</t>
+          <t>3802136,3802019,3802242,3802019,3802668,3802253,3802136,3802019,3802242,3802019,3802668,3802325,3802136,3802019,3802242,3802019,3802668,3802541,3802136,3802091,3802466,3802091,3802668,3802541,3802136,3802091,3802466,3802091,3802668,3802565,3802136,3802099,3802466,3802099,3802668,3802565,3802136,3802099,3802466,3802099,3802868,3802645,3802136,3802099,3802514,3802099,3802868,3802693,3802136,3802107,3802514,3802107,3802868,3802709,3802136,3802107,3802514,3802107,3802868,3802709,3802136,3802107,3802786,3802107,3802868,3803021,3802136,3802115,3802786,3802115,3802988,3802136,3802115,3802786,3802115,3802988,3802136,3802115,3802115,3802988,3802144,3802673,3802988,3802144,3802673,3802988,3802144,3802673,3802988,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802673,3802673,3802673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L18 W12/25; N=114; EHP=3782.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x31,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x6,heavy:127x1</t>
+          <t>L18 W12/25; N=114; EHP=9650.380461; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x5,medium:123x6,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3804136,3804673,3804242,3804019,3804668,3804253,3804136,3804673,3804242,3804019,3804668,3804325,3804136,3804673,3804242,3804019,3804668,3804541,3804136,3804673,3804242,3804091,3804668,3804541,3804136,3804673,3804466,3804091,3804668,3804565,3804136,3804673,3804466,3804091,3804668,3804645,3804136,3804673,3804466,3804099,3804868,3804645,3804136,3804673,3804514,3804099,3804868,3804693,3804136,3804673,3804514,3804099,3804868,3804693,3804136,3804673,3804514,3804107,3804868,3804709,3804136,3804673,3804514,3804107,3804868,3804709,3804136,3804673,3804786,3804107,3804868,3805021,3804136,3804673,3804786,3804115,3804988,3804136,3804673,3804786,3804115,3804988,3804136,3804673,3804988,3804144,3804673,3804988,3804144,3804673,3804988,3804144,3804673,3804988,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804673,3804673,3804673,3804673</t>
+          <t>3804136,3804019,3804242,3804019,3804668,3804253,3804136,3804019,3804242,3804019,3804668,3804325,3804136,3804019,3804242,3804019,3804668,3804541,3804136,3804091,3804242,3804091,3804668,3804541,3804136,3804091,3804466,3804091,3804668,3804565,3804136,3804091,3804466,3804091,3804668,3804645,3804136,3804099,3804466,3804099,3804868,3804645,3804136,3804099,3804514,3804099,3804868,3804693,3804136,3804099,3804514,3804099,3804868,3804693,3804136,3804107,3804514,3804107,3804868,3804709,3804136,3804107,3804514,3804107,3804868,3804709,3804136,3804107,3804786,3804107,3804868,3805021,3804136,3804115,3804786,3804115,3804988,3804136,3804115,3804786,3804115,3804988,3804136,3804673,3804988,3804144,3804673,3804988,3804144,3804673,3804988,3804144,3804673,3804988,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804673,3804673,3804673,3804673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L18 W13/25; N=120; EHP=4613.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x15,normal:18x14,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x33,heavy:86x2,heavy:88x2,fast:98x3,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L18 W13/25; N=120; EHP=11763.105309; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x4,fast:58x3,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3806136,3806673,3806242,3806019,3806668,3806253,3806136,3806673,3806242,3806019,3806668,3806253,3806136,3806673,3806242,3806019,3806668,3806325,3806136,3806673,3806242,3806091,3806668,3806541,3806136,3806673,3806466,3806091,3806668,3806565,3806136,3806673,3806466,3806091,3806668,3806645,3806136,3806673,3806466,3806099,3806868,3806645,3806136,3806673,3806466,3806099,3806868,3806693,3806136,3806673,3806514,3806099,3806868,3806693,3806136,3806673,3806514,3806107,3806868,3806709,3806136,3806673,3806514,3806107,3806868,3806709,3806136,3806673,3806786,3806107,3806868,3807021,3806136,3806673,3806786,3806115,3806988,3806136,3806673,3806786,3806115,3806988,3806136,3806673,3806786,3806115,3806988,3806144,3806673,3806988,3806144,3806673,3806988,3806144,3806673,3806988,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806673,3806673,3806673,3806673</t>
+          <t>3806136,3806019,3806242,3806019,3806668,3806253,3806136,3806019,3806242,3806019,3806668,3806253,3806136,3806019,3806242,3806019,3806668,3806325,3806136,3806091,3806242,3806091,3806668,3806541,3806136,3806091,3806466,3806091,3806668,3806565,3806136,3806091,3806466,3806091,3806668,3806645,3806136,3806099,3806466,3806099,3806868,3806645,3806136,3806099,3806466,3806099,3806868,3806693,3806136,3806099,3806514,3806099,3806868,3806693,3806136,3806107,3806514,3806107,3806868,3806709,3806136,3806107,3806514,3806107,3806868,3806709,3806136,3806107,3806786,3806107,3806868,3807021,3806136,3806115,3806786,3806115,3806988,3806136,3806115,3806786,3806115,3806988,3806136,3806115,3806786,3806115,3806988,3806144,3806673,3806988,3806144,3806673,3806988,3806144,3806673,3806988,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806673,3806673,3806673,3806673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L18 W14/25; N=126; EHP=5565.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x2,heavy:40x1,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x35,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L18 W14/25; N=126; EHP=14195.948481; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3808136,3808673,3808242,3808019,3808668,3808253,3808542,3808136,3808673,3808242,3808019,3808668,3808253,3808136,3808673,3808242,3808019,3808668,3808325,3808136,3808673,3808466,3808091,3808668,3808325,3808136,3808673,3808466,3808091,3808668,3808541,3808136,3808673,3808466,3808091,3808668,3808565,3808136,3808673,3808466,3808099,3808668,3808645,3808136,3808673,3808514,3808099,3808868,3808645,3808136,3808673,3808514,3808099,3808868,3808693,3808136,3808673,3808514,3808107,3808868,3808693,3808136,3808673,3808514,3808107,3808868,3808709,3808136,3808673,3808786,3808107,3808868,3809021,3808136,3808673,3808786,3808107,3808868,3809021,3808136,3808673,3808786,3808115,3808988,3808136,3808673,3808786,3808115,3808988,3808136,3808673,3808115,3808988,3808144,3808673,3808988,3808144,3808673,3808988,3808144,3808673,3808988,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808673,3808673,3808673,3808673</t>
+          <t>3808136,3808019,3808242,3808019,3808668,3808253,3808542,3808136,3808019,3808242,3808019,3808668,3808253,3808136,3808019,3808242,3808019,3808668,3808325,3808136,3808091,3808466,3808091,3808668,3808325,3808136,3808091,3808466,3808091,3808668,3808541,3808136,3808091,3808466,3808091,3808668,3808565,3808136,3808099,3808466,3808099,3808668,3808645,3808136,3808099,3808514,3808099,3808868,3808645,3808136,3808099,3808514,3808099,3808868,3808693,3808136,3808107,3808514,3808107,3808868,3808693,3808136,3808107,3808514,3808107,3808868,3808709,3808136,3808107,3808786,3808107,3808868,3809021,3808136,3808107,3808786,3808107,3808868,3809021,3808136,3808115,3808786,3808115,3808988,3808136,3808115,3808786,3808115,3808988,3808136,3808115,3808115,3808988,3808144,3808673,3808988,3808144,3808673,3808988,3808144,3808673,3808988,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808673,3808673,3808673,3808673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L18 W15/25; N=132; EHP=9713.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x16,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x36,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L18 W15/25; N=132; EHP=24772.990049; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3810136,3810673,3810242,3810019,3810668,3810253,3810136,3810673,3810242,3810019,3810668,3810253,3810136,3810673,3810242,3810019,3810668,3810325,3810136,3810673,3810242,3810091,3810668,3810325,3810136,3810673,3810466,3810091,3810668,3810541,3810136,3810673,3810466,3810091,3810668,3810565,3810136,3810673,3810466,3810091,3810868,3810565,3810136,3810673,3810466,3810099,3810868,3810645,3810136,3810673,3810514,3810099,3810868,3810693,3810136,3810673,3810514,3810099,3810868,3810693,3810136,3810673,3810514,3810107,3810868,3810709,3810136,3810673,3810514,3810107,3810868,3811021,3810136,3810673,3810786,3810107,3810868,3811021,3810136,3810673,3810786,3810115,3810988,3810136,3810673,3810786,3810115,3810988,3810136,3810673,3810786,3810115,3810988,3810136,3810673,3810115,3810988,3810144,3810673,3810988,3810144,3810673,3810988,3810144,3810673,3810988,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810673,3810673,3810673,3810673</t>
+          <t>3810136,3810019,3810242,3810019,3810668,3810253,3810136,3810019,3810242,3810019,3810668,3810253,3810136,3810019,3810242,3810019,3810668,3810325,3810136,3810091,3810242,3810091,3810668,3810325,3810136,3810091,3810466,3810091,3810668,3810541,3810136,3810091,3810466,3810091,3810668,3810565,3810136,3810091,3810466,3810091,3810868,3810565,3810136,3810099,3810466,3810099,3810868,3810645,3810136,3810099,3810514,3810099,3810868,3810693,3810136,3810099,3810514,3810099,3810868,3810693,3810136,3810107,3810514,3810107,3810868,3810709,3810136,3810107,3810514,3810107,3810868,3811021,3810136,3810107,3810786,3810107,3810868,3811021,3810136,3810115,3810786,3810115,3810988,3810136,3810115,3810786,3810115,3810988,3810136,3810115,3810786,3810115,3810988,3810136,3810115,3810115,3810988,3810144,3810673,3810988,3810144,3810673,3810988,3810144,3810673,3810988,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810673,3810673,3810673,3810673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L18 W16/25; N=138; EHP=9908.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x38,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L18 W16/25; N=138; EHP=25284.883215; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3812136,3812673,3812242,3812019,3812668,3812253,3812136,3812673,3812242,3812019,3812668,3812253,3812136,3812673,3812242,3812019,3812668,3812325,3812136,3812673,3812242,3812091,3812668,3812325,3812136,3812673,3812466,3812091,3812668,3812541,3812136,3812673,3812466,3812091,3812668,3812541,3812136,3812673,3812466,3812099,3812668,3812565,3812136,3812673,3812466,3812099,3812868,3812565,3812136,3812673,3812514,3812099,3812868,3812645,3812136,3812673,3812514,3812099,3812868,3812693,3812136,3812673,3812514,3812107,3812868,3812709,3812136,3812673,3812514,3812107,3812868,3812709,3812136,3812673,3812514,3812107,3812868,3813021,3812136,3812673,3812786,3812115,3812868,3813021,3812136,3812673,3812786,3812115,3812988,3812136,3812673,3812786,3812115,3812988,3812136,3812673,3812786,3812115,3812988,3812136,3812673,3812988,3812144,3812673,3812988,3812144,3812673,3812988,3812144,3812673,3812988,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812673,3812673,3812673,3812673,3812673</t>
+          <t>3812136,3812019,3812242,3812019,3812668,3812253,3812136,3812019,3812242,3812019,3812668,3812253,3812136,3812019,3812242,3812019,3812668,3812325,3812136,3812091,3812242,3812091,3812668,3812325,3812136,3812091,3812466,3812091,3812668,3812541,3812136,3812091,3812466,3812091,3812668,3812541,3812136,3812099,3812466,3812099,3812668,3812565,3812136,3812099,3812466,3812099,3812868,3812565,3812136,3812099,3812514,3812099,3812868,3812645,3812136,3812099,3812514,3812099,3812868,3812693,3812136,3812107,3812514,3812107,3812868,3812709,3812136,3812107,3812514,3812107,3812868,3812709,3812136,3812107,3812514,3812107,3812868,3813021,3812136,3812115,3812786,3812115,3812868,3813021,3812136,3812115,3812786,3812115,3812988,3812136,3812115,3812786,3812115,3812988,3812136,3812115,3812786,3812115,3812988,3812136,3812673,3812988,3812144,3812673,3812988,3812144,3812673,3812988,3812144,3812673,3812988,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812673,3812673,3812673,3812673,3812673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L18 W17/25; N=144; EHP=10107.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x40,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L18 W17/25; N=144; EHP=25778.399755; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3814136,3814673,3814242,3814019,3814668,3814253,3814136,3814673,3814242,3814019,3814668,3814325,3814136,3814673,3814242,3814019,3814668,3814325,3814136,3814673,3814242,3814019,3814668,3814541,3814136,3814673,3814242,3814091,3814668,3814541,3814136,3814673,3814466,3814091,3814668,3814565,3814136,3814673,3814466,3814091,3814668,3814565,3814136,3814673,3814466,3814099,3814668,3814645,3814136,3814673,3814466,3814099,3814868,3814645,3814136,3814673,3814514,3814099,3814868,3814693,3814136,3814673,3814514,3814099,3814868,3814693,3814136,3814673,3814514,3814107,3814868,3814709,3814136,3814673,3814514,3814107,3814868,3814709,3814136,3814673,3814786,3814107,3814868,3815021,3814136,3814673,3814786,3814107,3814868,3815021,3814136,3814673,3814786,3814115,3814988,3814136,3814673,3814786,3814115,3814988,3814144,3814673,3814786,3814115,3814988,3814144,3814673,3814988,3814144,3814673,3814988,3814144,3814673,3814988,3814144,3814673,3814988,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814673,3814673,3814673,3814673,3814673,3814673,3814673</t>
+          <t>3814136,3814019,3814242,3814019,3814668,3814253,3814136,3814019,3814242,3814019,3814668,3814325,3814136,3814019,3814242,3814019,3814668,3814325,3814136,3814019,3814242,3814019,3814668,3814541,3814136,3814091,3814242,3814091,3814668,3814541,3814136,3814091,3814466,3814091,3814668,3814565,3814136,3814091,3814466,3814091,3814668,3814565,3814136,3814099,3814466,3814099,3814668,3814645,3814136,3814099,3814466,3814099,3814868,3814645,3814136,3814099,3814514,3814099,3814868,3814693,3814136,3814099,3814514,3814099,3814868,3814693,3814136,3814107,3814514,3814107,3814868,3814709,3814136,3814107,3814514,3814107,3814868,3814709,3814136,3814107,3814786,3814107,3814868,3815021,3814136,3814107,3814786,3814107,3814868,3815021,3814136,3814115,3814786,3814115,3814988,3814136,3814115,3814786,3814115,3814988,3814144,3814115,3814786,3814115,3814988,3814144,3814673,3814988,3814144,3814673,3814988,3814144,3814673,3814988,3814144,3814673,3814988,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814673,3814673,3814673,3814673,3814673,3814673,3814673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L18 W18/25; N=150; EHP=10798.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x17,normal:18x18,fast:30x5,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L18 W18/25; N=150; EHP=27545.388628; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x7,normal:17x17,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3816136,3816673,3816242,3816019,3816668,3816253,3816136,3816673,3816242,3816019,3816668,3816253,3816136,3816673,3816242,3816019,3816668,3816325,3816136,3816673,3816242,3816019,3816668,3816541,3816136,3816673,3816466,3816091,3816668,3816541,3816136,3816673,3816466,3816091,3816668,3816565,3816136,3816673,3816466,3816091,3816668,3816565,3816136,3816673,3816466,3816091,3816868,3816645,3816136,3816673,3816466,3816099,3816868,3816645,3816136,3816673,3816514,3816099,3816868,3816693,3816136,3816673,3816514,3816099,3816868,3816693,3816136,3816673,3816514,3816107,3816868,3816709,3816136,3816673,3816514,3816107,3816868,3816709,3816136,3816673,3816786,3816107,3816868,3817021,3816136,3816673,3816786,3816107,3816868,3817021,3816136,3816673,3816786,3816115,3816988,3816136,3816673,3816786,3816115,3816988,3816136,3816673,3816786,3816115,3816988,3816136,3816673,3816115,3816988,3816144,3816673,3816988,3816144,3816673,3816988,3816144,3816673,3816988,3816144,3816673,3816988,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816673,3816673,3816673,3816673,3816673</t>
+          <t>3816136,3816019,3816242,3816019,3816668,3816253,3816136,3816019,3816242,3816019,3816668,3816253,3816136,3816019,3816242,3816019,3816668,3816325,3816136,3816019,3816242,3816019,3816668,3816541,3816136,3816091,3816466,3816091,3816668,3816541,3816136,3816091,3816466,3816091,3816668,3816565,3816136,3816091,3816466,3816091,3816668,3816565,3816136,3816091,3816466,3816091,3816868,3816645,3816136,3816099,3816466,3816099,3816868,3816645,3816136,3816099,3816514,3816099,3816868,3816693,3816136,3816099,3816514,3816099,3816868,3816693,3816136,3816107,3816514,3816107,3816868,3816709,3816136,3816107,3816514,3816107,3816868,3816709,3816136,3816107,3816786,3816107,3816868,3817021,3816136,3816107,3816786,3816107,3816868,3817021,3816136,3816115,3816786,3816115,3816988,3816136,3816115,3816786,3816115,3816988,3816136,3816115,3816786,3816115,3816988,3816136,3816115,3816115,3816988,3816144,3816673,3816988,3816144,3816673,3816988,3816144,3816673,3816988,3816144,3816673,3816988,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816673,3816673,3816673,3816673,3816673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L18 W19/25; N=156; EHP=12507.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L18 W19/25; N=156; EHP=31911.451049; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3818136,3818673,3818242,3818019,3818668,3818253,3818542,3818136,3818673,3818242,3818019,3818668,3818253,3818136,3818673,3818242,3818019,3818668,3818325,3818136,3818673,3818242,3818091,3818668,3818325,3818136,3818673,3818242,3818091,3818668,3818541,3818136,3818673,3818466,3818091,3818668,3818541,3818136,3818673,3818466,3818091,3818668,3818565,3818136,3818673,3818466,3818099,3818668,3818565,3818136,3818673,3818466,3818099,3818868,3818645,3818136,3818673,3818466,3818099,3818868,3818645,3818136,3818673,3818514,3818099,3818868,3818693,3818136,3818673,3818514,3818107,3818868,3818693,3818136,3818673,3818514,3818107,3818868,3818709,3818136,3818673,3818514,3818107,3818868,3818709,3818136,3818673,3818514,3818107,3818868,3819021,3818136,3818673,3818786,3818115,3818868,3819021,3818136,3818673,3818786,3818115,3818988,3818136,3818673,3818786,3818115,3818988,3818136,3818673,3818786,3818115,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818673,3818673,3818673,3818673,3818673,3818673,3818673</t>
+          <t>3818136,3818019,3818242,3818019,3818668,3818253,3818542,3818136,3818019,3818242,3818019,3818668,3818253,3818136,3818019,3818242,3818019,3818668,3818325,3818136,3818091,3818242,3818091,3818668,3818325,3818136,3818091,3818242,3818091,3818668,3818541,3818136,3818091,3818466,3818091,3818668,3818541,3818136,3818091,3818466,3818091,3818668,3818565,3818136,3818099,3818466,3818099,3818668,3818565,3818136,3818099,3818466,3818099,3818868,3818645,3818136,3818099,3818466,3818099,3818868,3818645,3818136,3818099,3818514,3818099,3818868,3818693,3818136,3818107,3818514,3818107,3818868,3818693,3818136,3818107,3818514,3818107,3818868,3818709,3818136,3818107,3818514,3818107,3818868,3818709,3818136,3818107,3818514,3818107,3818868,3819021,3818136,3818115,3818786,3818115,3818868,3819021,3818136,3818115,3818786,3818115,3818988,3818136,3818115,3818786,3818115,3818988,3818136,3818115,3818786,3818115,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818988,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818673,3818673,3818673,3818673,3818673,3818673,3818673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L18 W20/25; N=162; EHP=20997.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L18 W20/25; N=162; EHP=53534.547497; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10018214,10018224,10018216,10048640,10018223,10018217,10018214,10018224,10018216,10048640,10018223,10018217,10018214,10018224,10018216,10048640,10018223,10018218,10018214,10018224,10018216,10048640,10018223,10018218,10018214,10018224,10018216,10018211,10018223,10018221,10018214,10018224,10018219,10018211,10018223,10018221,10018214,10018224,10018219,10018211,10018223,10045197,10018214,10018224,10018219,10018211,10018223,10045197,10018214,10018224,10018219,10048641,10018223,10018222,10018214,10018224,10018219,10048641,10018228,10018222,10018214,10018224,10018220,10048641,10018228,10018225,10018214,10018224,10018220,10048641,10018228,10018225,10018214,10018224,10018220,10018212,10018228,10018226,10018214,10018224,10018220,10018212,10018228,10018226,10018214,10018224,10018220,10018212,10018228,10018230,10018214,10018224,10018227,10018212,10018228,10018230,10018214,10018224,10018227,10018213,10018228,10018214,10018224,10018227,10018213,10018229,10018214,10018224,10018227,10018213,10018229,10018214,10018224,10018227,10018213,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018224,10018224,10018224,10018224,10018224,10018224,10018224</t>
+          <t>10018214,10048640,10018216,10048640,10018223,10018217,10018214,10048640,10018216,10048640,10018223,10018217,10018214,10048640,10018216,10048640,10018223,10018218,10018214,10048640,10018216,10048640,10018223,10018218,10018214,10018211,10018216,10018211,10018223,10018221,10018214,10018211,10018219,10018211,10018223,10018221,10018214,10018211,10018219,10018211,10018223,10045197,10018214,10018211,10018219,10018211,10018223,10045197,10018214,10048641,10018219,10048641,10018223,10018222,10018214,10048641,10018219,10048641,10018228,10018222,10018214,10048641,10018220,10048641,10018228,10018225,10018214,10048641,10018220,10048641,10018228,10018225,10018214,10018212,10018220,10018212,10018228,10018226,10018214,10018212,10018220,10018212,10018228,10018226,10018214,10018212,10018220,10018212,10018228,10018230,10018214,10018212,10018227,10018212,10018228,10018230,10018214,10018213,10018227,10018213,10018228,10018214,10018213,10018227,10018213,10018229,10018214,10018213,10018227,10018213,10018229,10018214,10018213,10018227,10018213,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018229,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018215,10018224,10018224,10018224,10018224,10018224,10018224,10018224,10018224</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L18 W21/25; N=168; EHP=21417.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L18 W21/25; N=168; EHP=54631.274147; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10018234,10018244,10018236,10048642,10018243,10018237,10018234,10018244,10018236,10048642,10018243,10018237,10018234,10018244,10018236,10048642,10018243,10018238,10018234,10018244,10018236,10048642,10018243,10018238,10018234,10018244,10018236,10018231,10018243,10045198,10018234,10018244,10018239,10018231,10018243,10045198,10018234,10018244,10018239,10018231,10018243,10018241,10018234,10018244,10018239,10018231,10018243,10018241,10018234,10018244,10018239,10048643,10018248,10018242,10018234,10018244,10018239,10048643,10018248,10018242,10018234,10018244,10018240,10048643,10018248,10018245,10018234,10018244,10018240,10048643,10018248,10018245,10018234,10018244,10018240,10018232,10018248,10018246,10018234,10018244,10018240,10018232,10018248,10018246,10018234,10018244,10018240,10018232,10018248,10018246,10018234,10018244,10018247,10018232,10018248,10018250,10018234,10018244,10018247,10018233,10018248,10018250,10018234,10018244,10018247,10018233,10018249,10018234,10018244,10018247,10018233,10018249,10018234,10018244,10018247,10018233,10018249,10018234,10018244,10018233,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018244,10018244,10018244,10018244,10018244,10018244</t>
+          <t>10018234,10048642,10018236,10048642,10018243,10018237,10018234,10048642,10018236,10048642,10018243,10018237,10018234,10048642,10018236,10048642,10018243,10018238,10018234,10048642,10018236,10048642,10018243,10018238,10018234,10018231,10018236,10018231,10018243,10045198,10018234,10018231,10018239,10018231,10018243,10045198,10018234,10018231,10018239,10018231,10018243,10018241,10018234,10018231,10018239,10018231,10018243,10018241,10018234,10048643,10018239,10048643,10018248,10018242,10018234,10048643,10018239,10048643,10018248,10018242,10018234,10048643,10018240,10048643,10018248,10018245,10018234,10048643,10018240,10048643,10018248,10018245,10018234,10018232,10018240,10018232,10018248,10018246,10018234,10018232,10018240,10018232,10018248,10018246,10018234,10018232,10018240,10018232,10018248,10018246,10018234,10018232,10018247,10018232,10018248,10018250,10018234,10018233,10018247,10018233,10018248,10018250,10018234,10018233,10018247,10018233,10018249,10018234,10018233,10018247,10018233,10018249,10018234,10018233,10018247,10018233,10018249,10018234,10018233,10018233,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018249,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018235,10018244,10018244,10018244,10018244,10018244,10018244,10018244</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L18 W22/25; N=174; EHP=21846.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x48,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L18 W22/25; N=174; EHP=55731.557772; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x8,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10018254,10018265,10018256,10048644,10018264,10018257,10018254,10018265,10018256,10048644,10018264,10018257,10018254,10018265,10018256,10048644,10018264,10018258,10018254,10018265,10018256,10048644,10018264,10018258,10018254,10018265,10018256,10048644,10018264,10018261,10018254,10018265,10018259,10018251,10018264,10018261,10018254,10018265,10018259,10018251,10018264,10018262,10018254,10018265,10018259,10018251,10018264,10018262,10018254,10018265,10018259,10018251,10018264,10018263,10018254,10018265,10018259,10048645,10018268,10018263,10018254,10018265,10018260,10048645,10018268,10018263,10018254,10018265,10018260,10048645,10018268,10018266,10018254,10018265,10018260,10048645,10018268,10018266,10018254,10018265,10018260,10048645,10018268,10018266,10018254,10018265,10018260,10018252,10018268,10045199,10018254,10018265,10018267,10018252,10018268,10045199,10018254,10018265,10018267,10018252,10018268,10018270,10018254,10018265,10018267,10018252,10018268,10018270,10018254,10018265,10018267,10018253,10018269,10018254,10018265,10018267,10018253,10018269,10018254,10018265,10018267,10018253,10018269,10018255,10018265,10018253,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018265,10018265,10018265,10018265,10018265,10018265,10018265,10018265</t>
+          <t>10018254,10048644,10018256,10048644,10018264,10018257,10018254,10048644,10018256,10048644,10018264,10018257,10018254,10048644,10018256,10048644,10018264,10018258,10018254,10048644,10018256,10048644,10018264,10018258,10018254,10048644,10018256,10048644,10018264,10018261,10018254,10018251,10018259,10018251,10018264,10018261,10018254,10018251,10018259,10018251,10018264,10018262,10018254,10018251,10018259,10018251,10018264,10018262,10018254,10018251,10018259,10018251,10018264,10018263,10018254,10048645,10018259,10048645,10018268,10018263,10018254,10048645,10018260,10048645,10018268,10018263,10018254,10048645,10018260,10048645,10018268,10018266,10018254,10048645,10018260,10048645,10018268,10018266,10018254,10048645,10018260,10048645,10018268,10018266,10018254,10018252,10018260,10018252,10018268,10045199,10018254,10018252,10018267,10018252,10018268,10045199,10018254,10018252,10018267,10018252,10018268,10018270,10018254,10018252,10018267,10018252,10018268,10018270,10018254,10018253,10018267,10018253,10018269,10018254,10018253,10018267,10018253,10018269,10018254,10018253,10018267,10018253,10018269,10018255,10018253,10018253,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018269,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018255,10018265,10018265,10018265,10018265,10018265,10018265,10018265,10018265,10018265</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L18 W23/25; N=180; EHP=22283.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x50,heavy:86x3,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L18 W23/25; N=180; EHP=56853.782857; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10018274,10018285,10018276,10048646,10018284,10018277,10018274,10018285,10018276,10048646,10018284,10018277,10018274,10018285,10018276,10048646,10018284,10018277,10018274,10018285,10018276,10048646,10018284,10018278,10018274,10018285,10018276,10048646,10018284,10018278,10018274,10018285,10018279,10018271,10018284,10018281,10018274,10018285,10018279,10018271,10018284,10018281,10018274,10018285,10018279,10018271,10018284,10018282,10018274,10018285,10018279,10018271,10018284,10018282,10018274,10018285,10018279,10048647,10018289,10018283,10018274,10018285,10018279,10048647,10018289,10018283,10018274,10018285,10018280,10048647,10018289,10018286,10018274,10018285,10018280,10048647,10018289,10018286,10018274,10018285,10018280,10018272,10018289,10018286,10018274,10018285,10018280,10018272,10018289,10018287,10018274,10018285,10018280,10018272,10018289,10018287,10018274,10018285,10018280,10018272,10018289,10018291,10018274,10018285,10018288,10018272,10018289,10018291,10018274,10018285,10018288,10018273,10018290,10018274,10018285,10018288,10018273,10018290,10018274,10018285,10018288,10018273,10018290,10018274,10018285,10018288,10018273,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018285,10018285,10018285,10018285,10018285,10018285,10018285</t>
+          <t>10018274,10048646,10018276,10048646,10018284,10018277,10018274,10048646,10018276,10048646,10018284,10018277,10018274,10048646,10018276,10048646,10018284,10018277,10018274,10048646,10018276,10048646,10018284,10018278,10018274,10048646,10018276,10048646,10018284,10018278,10018274,10018271,10018279,10018271,10018284,10018281,10018274,10018271,10018279,10018271,10018284,10018281,10018274,10018271,10018279,10018271,10018284,10018282,10018274,10018271,10018279,10018271,10018284,10018282,10018274,10048647,10018279,10048647,10018289,10018283,10018274,10048647,10018279,10048647,10018289,10018283,10018274,10048647,10018280,10048647,10018289,10018286,10018274,10048647,10018280,10048647,10018289,10018286,10018274,10018272,10018280,10018272,10018289,10018286,10018274,10018272,10018280,10018272,10018289,10018287,10018274,10018272,10018280,10018272,10018289,10018287,10018274,10018272,10018280,10018272,10018289,10018291,10018274,10018272,10018288,10018272,10018289,10018291,10018274,10018273,10018288,10018273,10018290,10018274,10018273,10018288,10018273,10018290,10018274,10018273,10018288,10018273,10018290,10018274,10018273,10018288,10018273,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018290,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018275,10018285,10018285,10018285,10018285,10018285,10018285,10018285,10018285</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L18 W24/25; N=186; EHP=23861.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x23,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x3,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L18 W24/25; N=186; EHP=60861.133486; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x6,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10018295,10018306,10018297,10048648,10018305,10018298,10018313,10018295,10018306,10018297,10048648,10018305,10018298,10018295,10018306,10018297,10048648,10018305,10018298,10018295,10018306,10018297,10048648,10018305,10018299,10018295,10018306,10018297,10018292,10018305,10018299,10018295,10018306,10018297,10018292,10018305,10018299,10018295,10018306,10018300,10018292,10018305,10018302,10018295,10018306,10018300,10018292,10018305,10018302,10018295,10018306,10018300,10018292,10018305,10018303,10018295,10018306,10018300,10048649,10018310,10018303,10018295,10018306,10018300,10048649,10018310,10018304,10018295,10018306,10018301,10048649,10018310,10018304,10018295,10018306,10018301,10048649,10018310,10018307,10018295,10018306,10018301,10018293,10018310,10018307,10018295,10018306,10018301,10018293,10018310,10018308,10018295,10018306,10018301,10018293,10018310,10018308,10018295,10018306,10018301,10018293,10018310,10018312,10018295,10018306,10018309,10018293,10018310,10018312,10018295,10018306,10018309,10018294,10018311,10018312,10018295,10018306,10018309,10018294,10018311,10018295,10018306,10018309,10018294,10018311,10018295,10018306,10018309,10018294,10018311,10018295,10018306,10018309,10018294,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018306,10018306,10018306,10018306,10018306,10018306,10018306,10018306</t>
+          <t>10018295,10048648,10018297,10048648,10018305,10018298,10018313,10018295,10048648,10018297,10048648,10018305,10018298,10018295,10048648,10018297,10048648,10018305,10018298,10018295,10048648,10018297,10048648,10018305,10018299,10018295,10018292,10018297,10018292,10018305,10018299,10018295,10018292,10018297,10018292,10018305,10018299,10018295,10018292,10018300,10018292,10018305,10018302,10018295,10018292,10018300,10018292,10018305,10018302,10018295,10018292,10018300,10018292,10018305,10018303,10018295,10048649,10018300,10048649,10018310,10018303,10018295,10048649,10018300,10048649,10018310,10018304,10018295,10048649,10018301,10048649,10018310,10018304,10018295,10048649,10018301,10048649,10018310,10018307,10018295,10018293,10018301,10018293,10018310,10018307,10018295,10018293,10018301,10018293,10018310,10018308,10018295,10018293,10018301,10018293,10018310,10018308,10018295,10018293,10018301,10018293,10018310,10018312,10018295,10018293,10018309,10018293,10018310,10018312,10018295,10018294,10018309,10018294,10018311,10018312,10018295,10018294,10018309,10018294,10018311,10018295,10018294,10018309,10018294,10018311,10018295,10018294,10018309,10018294,10018311,10018295,10018294,10018309,10018294,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018311,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018296,10018306,10018306,10018306,10018306,10018306,10018306,10018306,10018306,10018306</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L18 W25/25; N=192; EHP=47625.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x23,normal:18x22,fast:30x6,heavy:31x3,heavy:40x3,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x53,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x10,heavy:127x3,boss:132x1</t>
+          <t>L18 W25/25; N=192; EHP=121460.857845; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x5,fast:64x6,fast:98x6,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x10,normal:17x23,normal:18x22,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L18/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L18/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>246</v>
+        <v>340</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>218</v>
+        <v>290</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>211</v>
+        <v>350</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>190</v>
+        <v>290</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>176</v>
+        <v>290</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>169</v>
+        <v>350</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>162</v>
+        <v>280</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>155</v>
+        <v>260</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>141</v>
+        <v>290</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
